--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -447,7 +447,7 @@
         <v>19283</v>
       </c>
       <c r="C2" t="n">
-        <v>63694</v>
+        <v>19283</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         <v>50305</v>
       </c>
       <c r="C3" t="n">
-        <v>63694</v>
+        <v>50305</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         <v>54331</v>
       </c>
       <c r="C4" t="n">
-        <v>62298</v>
+        <v>54331</v>
       </c>
     </row>
     <row r="5">
@@ -485,7 +485,9 @@
       <c r="B5" t="n">
         <v>58220</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>58220</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -497,7 +499,7 @@
         <v>58927</v>
       </c>
       <c r="C6" t="n">
-        <v>63694</v>
+        <v>58927</v>
       </c>
     </row>
     <row r="7">
@@ -510,7 +512,7 @@
         <v>61856</v>
       </c>
       <c r="C7" t="n">
-        <v>63694</v>
+        <v>61856</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +525,7 @@
         <v>61992</v>
       </c>
       <c r="C8" t="n">
-        <v>62298</v>
+        <v>64413</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +538,7 @@
         <v>62034</v>
       </c>
       <c r="C9" t="n">
-        <v>62298</v>
+        <v>62034</v>
       </c>
     </row>
     <row r="10">
@@ -549,7 +551,7 @@
         <v>62288</v>
       </c>
       <c r="C10" t="n">
-        <v>63694</v>
+        <v>62288</v>
       </c>
     </row>
     <row r="11">
@@ -575,7 +577,7 @@
         <v>62336</v>
       </c>
       <c r="C12" t="n">
-        <v>63807</v>
+        <v>62336</v>
       </c>
     </row>
     <row r="13">
@@ -588,7 +590,7 @@
         <v>62358</v>
       </c>
       <c r="C13" t="n">
-        <v>62298</v>
+        <v>62358</v>
       </c>
     </row>
     <row r="14">
@@ -600,9 +602,7 @@
       <c r="B14" t="n">
         <v>62380</v>
       </c>
-      <c r="C14" t="n">
-        <v>62578</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,9 +613,7 @@
       <c r="B15" t="n">
         <v>62401</v>
       </c>
-      <c r="C15" t="n">
-        <v>62578</v>
-      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -627,7 +625,7 @@
         <v>62436</v>
       </c>
       <c r="C16" t="n">
-        <v>63807</v>
+        <v>61856</v>
       </c>
     </row>
     <row r="17">
@@ -640,7 +638,7 @@
         <v>62440</v>
       </c>
       <c r="C17" t="n">
-        <v>62298</v>
+        <v>62440</v>
       </c>
     </row>
     <row r="18">
@@ -653,7 +651,7 @@
         <v>62485</v>
       </c>
       <c r="C18" t="n">
-        <v>19283</v>
+        <v>62445</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +664,7 @@
         <v>62578</v>
       </c>
       <c r="C19" t="n">
-        <v>63694</v>
+        <v>62578</v>
       </c>
     </row>
     <row r="20">
@@ -679,7 +677,7 @@
         <v>62598</v>
       </c>
       <c r="C20" t="n">
-        <v>62306</v>
+        <v>62598</v>
       </c>
     </row>
     <row r="21">
@@ -692,7 +690,7 @@
         <v>62616</v>
       </c>
       <c r="C21" t="n">
-        <v>62336</v>
+        <v>62616</v>
       </c>
     </row>
     <row r="22">
@@ -705,7 +703,7 @@
         <v>62645</v>
       </c>
       <c r="C22" t="n">
-        <v>62645</v>
+        <v>63807</v>
       </c>
     </row>
     <row r="23">
@@ -718,7 +716,7 @@
         <v>9001</v>
       </c>
       <c r="C23" t="n">
-        <v>63807</v>
+        <v>62760</v>
       </c>
     </row>
     <row r="24">
@@ -730,9 +728,7 @@
       <c r="B24" t="n">
         <v>63629</v>
       </c>
-      <c r="C24" t="n">
-        <v>62336</v>
-      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -743,9 +739,7 @@
       <c r="B25" t="n">
         <v>63202</v>
       </c>
-      <c r="C25" t="n">
-        <v>62306</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -757,7 +751,7 @@
         <v>63273</v>
       </c>
       <c r="C26" t="n">
-        <v>63694</v>
+        <v>63273</v>
       </c>
     </row>
     <row r="27">
@@ -770,7 +764,7 @@
         <v>63694</v>
       </c>
       <c r="C27" t="n">
-        <v>62421</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="28">
@@ -783,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>19283</v>
+        <v>63807</v>
       </c>
     </row>
     <row r="29">
@@ -796,7 +790,7 @@
         <v>63836</v>
       </c>
       <c r="C29" t="n">
-        <v>62572</v>
+        <v>61856</v>
       </c>
     </row>
     <row r="30">
@@ -809,7 +803,7 @@
         <v>63887</v>
       </c>
       <c r="C30" t="n">
-        <v>63694</v>
+        <v>62445</v>
       </c>
     </row>
     <row r="31">
@@ -821,9 +815,7 @@
       <c r="B31" t="n">
         <v>64413</v>
       </c>
-      <c r="C31" t="n">
-        <v>63694</v>
-      </c>
+      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -835,7 +827,7 @@
         <v>65442</v>
       </c>
       <c r="C32" t="n">
-        <v>62298</v>
+        <v>65444</v>
       </c>
     </row>
     <row r="33">
@@ -848,7 +840,7 @@
         <v>75012</v>
       </c>
       <c r="C33" t="n">
-        <v>62298</v>
+        <v>75012</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,328 +518,289 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_61992.jpg</t>
+          <t>EXAM_FORM1_62034.jpeg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61992</v>
+        <v>62034</v>
       </c>
       <c r="C8" t="n">
-        <v>64413</v>
+        <v>62034</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62034.jpeg</t>
+          <t>EXAM_FORM1_62298.jpeg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62034</v>
+        <v>62298</v>
       </c>
       <c r="C9" t="n">
-        <v>62034</v>
+        <v>62298</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62288.png</t>
+          <t>EXAM_FORM1_62358.jpeg</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62288</v>
+        <v>62358</v>
       </c>
       <c r="C10" t="n">
-        <v>62288</v>
+        <v>62358</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62298.jpeg</t>
+          <t>EXAM_FORM1_62380.jpeg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62298</v>
-      </c>
-      <c r="C11" t="n">
-        <v>62298</v>
-      </c>
+        <v>62380</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62336.JPG</t>
+          <t>EXAM_FORM1_62401.jpg</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62336</v>
-      </c>
-      <c r="C12" t="n">
-        <v>62336</v>
-      </c>
+        <v>62401</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62358.jpeg</t>
+          <t>EXAM_FORM1_62436.jpeg</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62358</v>
+        <v>62436</v>
       </c>
       <c r="C13" t="n">
-        <v>62358</v>
+        <v>61856</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62380.jpeg</t>
+          <t>EXAM_FORM1_62440.jpeg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62380</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>62440</v>
+      </c>
+      <c r="C14" t="n">
+        <v>62440</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62401.jpg</t>
+          <t>EXAM_FORM1_62445.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62401</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>62485</v>
+      </c>
+      <c r="C15" t="n">
+        <v>62445</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62436.jpeg</t>
+          <t>EXAM_FORM1_62578.jpg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62436</v>
+        <v>62578</v>
       </c>
       <c r="C16" t="n">
-        <v>61856</v>
+        <v>62578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62440.jpeg</t>
+          <t>EXAM_FORM1_62598.jpg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>62440</v>
+        <v>62598</v>
       </c>
       <c r="C17" t="n">
-        <v>62440</v>
+        <v>62598</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62445.jpg</t>
+          <t>EXAM_FORM1_62616.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62485</v>
+        <v>62616</v>
       </c>
       <c r="C18" t="n">
-        <v>62445</v>
+        <v>62616</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62578.jpg</t>
+          <t>EXAM_FORM1_62645.jpeg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62578</v>
+        <v>62645</v>
       </c>
       <c r="C19" t="n">
-        <v>62578</v>
+        <v>63807</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62598.jpg</t>
+          <t>EXAM_FORM1_62766.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>62598</v>
+        <v>9001</v>
       </c>
       <c r="C20" t="n">
-        <v>62598</v>
+        <v>62760</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62616.jpg</t>
+          <t>EXAM_FORM1_63029.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62616</v>
-      </c>
-      <c r="C21" t="n">
-        <v>62616</v>
-      </c>
+        <v>63629</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62645.jpeg</t>
+          <t>EXAM_FORM1_63272.jpg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62645</v>
-      </c>
-      <c r="C22" t="n">
-        <v>63807</v>
-      </c>
+        <v>63202</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62766.jpg</t>
+          <t>EXAM_FORM1_63273.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9001</v>
+        <v>63273</v>
       </c>
       <c r="C23" t="n">
-        <v>62760</v>
+        <v>63273</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63029.jpg</t>
+          <t>EXAM_FORM1_63694.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63629</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>63694</v>
+      </c>
+      <c r="C24" t="n">
+        <v>63694</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63272.jpg</t>
+          <t>EXAM_FORM1_63807.jpeg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63202</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>63807</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63273.jpg</t>
+          <t>EXAM_FORM1_63836.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63273</v>
+        <v>63836</v>
       </c>
       <c r="C26" t="n">
-        <v>63273</v>
+        <v>61856</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63694.jpg</t>
+          <t>EXAM_FORM1_63887.jpeg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63694</v>
+        <v>63887</v>
       </c>
       <c r="C27" t="n">
-        <v>63694</v>
+        <v>62445</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63807.jpeg</t>
+          <t>EXAM_FORM1_64413.jpg</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>63807</v>
-      </c>
+        <v>64413</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63836.jpg</t>
+          <t>EXAM_FORM1_65442.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>63836</v>
+        <v>65442</v>
       </c>
       <c r="C29" t="n">
-        <v>61856</v>
+        <v>65444</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63887.jpeg</t>
+          <t>EXAM_FORM1_75012.jpg</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63887</v>
+        <v>75012</v>
       </c>
       <c r="C30" t="n">
-        <v>62445</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>EXAM_FORM1_64413.jpg</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>64413</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>EXAM_FORM1_65442.jpg</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>65442</v>
-      </c>
-      <c r="C32" t="n">
-        <v>65444</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>EXAM_FORM1_75012.jpg</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>75012</v>
-      </c>
-      <c r="C33" t="n">
         <v>75012</v>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_PRESENCES.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -518,289 +518,328 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62034.jpeg</t>
+          <t>EXAM_FORM1_61992.jpg</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62034</v>
+        <v>61992</v>
       </c>
       <c r="C8" t="n">
-        <v>62034</v>
+        <v>64413</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62298.jpeg</t>
+          <t>EXAM_FORM1_62034.jpeg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62298</v>
+        <v>62034</v>
       </c>
       <c r="C9" t="n">
-        <v>62298</v>
+        <v>62034</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62358.jpeg</t>
+          <t>EXAM_FORM1_62288.png</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62358</v>
+        <v>62288</v>
       </c>
       <c r="C10" t="n">
-        <v>62358</v>
+        <v>62288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62380.jpeg</t>
+          <t>EXAM_FORM1_62298.jpeg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62380</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>62298</v>
+      </c>
+      <c r="C11" t="n">
+        <v>62298</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62401.jpg</t>
+          <t>EXAM_FORM1_62336.JPG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62401</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>62336</v>
+      </c>
+      <c r="C12" t="n">
+        <v>62336</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62436.jpeg</t>
+          <t>EXAM_FORM1_62358.jpeg</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62436</v>
+        <v>62358</v>
       </c>
       <c r="C13" t="n">
-        <v>61856</v>
+        <v>62358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62440.jpeg</t>
+          <t>EXAM_FORM1_62380.jpeg</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62440</v>
-      </c>
-      <c r="C14" t="n">
-        <v>62440</v>
-      </c>
+        <v>62380</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62445.jpg</t>
+          <t>EXAM_FORM1_62401.jpg</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>62485</v>
-      </c>
-      <c r="C15" t="n">
-        <v>62445</v>
-      </c>
+        <v>62401</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62578.jpg</t>
+          <t>EXAM_FORM1_62436.jpeg</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62578</v>
+        <v>62436</v>
       </c>
       <c r="C16" t="n">
-        <v>62578</v>
+        <v>61856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62598.jpg</t>
+          <t>EXAM_FORM1_62440.jpeg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>62598</v>
+        <v>62440</v>
       </c>
       <c r="C17" t="n">
-        <v>62598</v>
+        <v>62440</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62616.jpg</t>
+          <t>EXAM_FORM1_62445.jpg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62616</v>
+        <v>62485</v>
       </c>
       <c r="C18" t="n">
-        <v>62616</v>
+        <v>62445</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62645.jpeg</t>
+          <t>EXAM_FORM1_62578.jpg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62645</v>
+        <v>62578</v>
       </c>
       <c r="C19" t="n">
-        <v>63807</v>
+        <v>62578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_62766.jpg</t>
+          <t>EXAM_FORM1_62598.jpg</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9001</v>
+        <v>62598</v>
       </c>
       <c r="C20" t="n">
-        <v>62760</v>
+        <v>62598</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63029.jpg</t>
+          <t>EXAM_FORM1_62616.jpg</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63629</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>62616</v>
+      </c>
+      <c r="C21" t="n">
+        <v>62616</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63272.jpg</t>
+          <t>EXAM_FORM1_62645.jpeg</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63202</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>62645</v>
+      </c>
+      <c r="C22" t="n">
+        <v>63807</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63273.jpg</t>
+          <t>EXAM_FORM1_62766.jpg</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63273</v>
+        <v>9001</v>
       </c>
       <c r="C23" t="n">
-        <v>63273</v>
+        <v>62760</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63694.jpg</t>
+          <t>EXAM_FORM1_63029.jpg</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63694</v>
-      </c>
-      <c r="C24" t="n">
-        <v>63694</v>
-      </c>
+        <v>63629</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63807.jpeg</t>
+          <t>EXAM_FORM1_63272.jpg</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="n">
-        <v>63807</v>
-      </c>
+        <v>63202</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63836.jpg</t>
+          <t>EXAM_FORM1_63273.jpg</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63836</v>
+        <v>63273</v>
       </c>
       <c r="C26" t="n">
-        <v>61856</v>
+        <v>63273</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_63887.jpeg</t>
+          <t>EXAM_FORM1_63694.jpg</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63887</v>
+        <v>63694</v>
       </c>
       <c r="C27" t="n">
-        <v>62445</v>
+        <v>63694</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_64413.jpg</t>
+          <t>EXAM_FORM1_63807.jpeg</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64413</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>63807</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EXAM_FORM1_65442.jpg</t>
+          <t>EXAM_FORM1_63836.jpg</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65442</v>
+        <v>63836</v>
       </c>
       <c r="C29" t="n">
-        <v>65444</v>
+        <v>61856</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>EXAM_FORM1_63887.jpeg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>63887</v>
+      </c>
+      <c r="C30" t="n">
+        <v>62445</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EXAM_FORM1_64413.jpg</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>64413</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EXAM_FORM1_65442.jpg</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>65442</v>
+      </c>
+      <c r="C32" t="n">
+        <v>65444</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>EXAM_FORM1_75012.jpg</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B33" t="n">
         <v>75012</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C33" t="n">
         <v>75012</v>
       </c>
     </row>
